--- a/extension/results/fair_cut/qaoa_vs_lp.xlsx
+++ b/extension/results/fair_cut/qaoa_vs_lp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2" conformance="strict">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevehalley/Code/Github/QuantumHypergraphPartitioning/extension/results/fair_cut/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevehalley/Code/GitHub/QuantumHypergraphPartitioning/extension/results/fair_cut/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_missing-docid_{18CF43FD-24A6-C54E-B573-F8C3590160A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{E197D1F8-D6DF-AA41-A3D6-7FA7BC3B872D}"/>
+    <workbookView xWindow="760" yWindow="600" windowWidth="28040" windowHeight="16100" xr2:uid="{E197D1F8-D6DF-AA41-A3D6-7FA7BC3B872D}"/>
   </bookViews>
   <sheets>
     <sheet name="comparison" sheetId="4" r:id="rId1"/>
@@ -7299,7 +7299,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -7784,8 +7784,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -10034,7 +10034,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>9</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>9</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>9</v>
       </c>
@@ -10121,7 +10121,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -10150,7 +10150,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>9</v>
       </c>
@@ -10179,7 +10179,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>9</v>
       </c>
@@ -10208,7 +10208,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>9</v>
       </c>
@@ -10237,7 +10237,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>9</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>9</v>
       </c>
@@ -10295,7 +10295,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>9</v>
       </c>
@@ -10353,7 +10353,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>9</v>
       </c>
@@ -10382,7 +10382,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -10411,7 +10411,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>9</v>
       </c>
@@ -10440,7 +10440,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>9</v>
       </c>
@@ -10469,7 +10469,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -10498,7 +10498,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>9</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>9</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>9</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>9</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>9</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>9</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>9</v>
       </c>
